--- a/data/FOMC_meeting_dates.xlsx
+++ b/data/FOMC_meeting_dates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/albert/Documents/1_Economics/Research/UMP/Empirical Part/Shocks/Update Wieland-Yang/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/albert/Dropbox/0_Research/Active/UMP/Empirical Part/Generate MP Shocks/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E809D9-7963-ED49-9EA4-E160C702D3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF724B2-5A3D-1D4A-9AEF-DAEE9160831D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{B9A83CF8-72FC-0549-BD41-DF56A5AAA2DF}"/>
   </bookViews>
@@ -417,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94076105-8E28-8943-8ECC-0A8D74DF60F0}">
-  <dimension ref="A1:D449"/>
+  <dimension ref="A1:D465"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -5807,6 +5807,182 @@
       </c>
       <c r="D449" s="1"/>
     </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A450">
+        <v>2019</v>
+      </c>
+      <c r="B450">
+        <v>1</v>
+      </c>
+      <c r="C450">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A451">
+        <v>2019</v>
+      </c>
+      <c r="B451">
+        <v>3</v>
+      </c>
+      <c r="C451">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A452">
+        <v>2019</v>
+      </c>
+      <c r="B452">
+        <v>5</v>
+      </c>
+      <c r="C452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A453">
+        <v>2019</v>
+      </c>
+      <c r="B453">
+        <v>6</v>
+      </c>
+      <c r="C453">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A454">
+        <v>2019</v>
+      </c>
+      <c r="B454">
+        <v>7</v>
+      </c>
+      <c r="C454">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A455">
+        <v>2019</v>
+      </c>
+      <c r="B455">
+        <v>9</v>
+      </c>
+      <c r="C455">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A456">
+        <v>2019</v>
+      </c>
+      <c r="B456">
+        <v>10</v>
+      </c>
+      <c r="C456">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A457">
+        <v>2019</v>
+      </c>
+      <c r="B457">
+        <v>12</v>
+      </c>
+      <c r="C457">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A458">
+        <v>2020</v>
+      </c>
+      <c r="B458">
+        <v>1</v>
+      </c>
+      <c r="C458">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A459">
+        <v>2020</v>
+      </c>
+      <c r="B459">
+        <v>3</v>
+      </c>
+      <c r="C459">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A460">
+        <v>2020</v>
+      </c>
+      <c r="B460">
+        <v>4</v>
+      </c>
+      <c r="C460">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A461">
+        <v>2020</v>
+      </c>
+      <c r="B461">
+        <v>6</v>
+      </c>
+      <c r="C461">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A462">
+        <v>2020</v>
+      </c>
+      <c r="B462">
+        <v>7</v>
+      </c>
+      <c r="C462">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A463">
+        <v>2020</v>
+      </c>
+      <c r="B463">
+        <v>9</v>
+      </c>
+      <c r="C463">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A464">
+        <v>2020</v>
+      </c>
+      <c r="B464">
+        <v>11</v>
+      </c>
+      <c r="C464">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A465">
+        <v>2020</v>
+      </c>
+      <c r="B465">
+        <v>12</v>
+      </c>
+      <c r="C465">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
